--- a/public/管理口径原因分析默认模版/无锡宜兴项目.xlsx
+++ b/public/管理口径原因分析默认模版/无锡宜兴项目.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1581" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1581" uniqueCount="191">
   <si>
     <t>工作表目录</t>
   </si>
@@ -136,7 +136,7 @@
     <t>苏州销售太仓实训基地</t>
   </si>
   <si>
-    <t>合计预算执行分析（2026年07月）</t>
+    <t>合计预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>项目</t>
@@ -191,7 +191,7 @@
     <t xml:space="preserve">     减:（一）经营性采购支出</t>
   </si>
   <si>
-    <t>上年因ERP上线提前关账，进入6个月的成本，本年是正常入7个月成本</t>
+    <t>上年因ERP上线提前关账，进入7个月的成本，本年是正常入8个月成本</t>
   </si>
   <si>
     <t>本年预计的采购支出未达到预期</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">        （三）经营性税费</t>
   </si>
   <si>
-    <t>正常经营需缴纳的税款</t>
+    <t>本年整租租金未收亦未开票，因此税费相应减少</t>
   </si>
   <si>
     <t xml:space="preserve">        （四）油气分成支出</t>
@@ -246,6 +246,12 @@
   </si>
   <si>
     <t xml:space="preserve">        （六）外包劳务支出</t>
+  </si>
+  <si>
+    <t>上年无锡销售有32个加油站的项目，因此人工同比去年减少</t>
+  </si>
+  <si>
+    <t>本年预算基数以项目合同测算表为基数，实际经营过程中目前存在使用退休返聘人员等情况，致使人工成本收入未完全按照测算表进度推进，若后续业主方要求更换人员，结余费用需进行使用，如替换缴纳社保人员。及此项目（高温、劳保、体检）三项费用，预算时为全年每月均摊，实际截至8月仅发生了高温费。</t>
   </si>
   <si>
     <t xml:space="preserve">        （七）维修费</t>
@@ -308,7 +314,10 @@
     <t xml:space="preserve">        （十六）信用减值损失</t>
   </si>
   <si>
-    <t>信用减值损失的增加是因为本年有306万应收账款账龄超过1年，信用减值计提了74.17万。</t>
+    <t>信用减值损失的增加是因为本年有353万应收账款账龄超过1年</t>
+  </si>
+  <si>
+    <t>信用减值损失的增加是因为本年有353万应收账款账龄超过1年，信用减值计提了85.54万。</t>
   </si>
   <si>
     <t xml:space="preserve">        （十七）存货差额调整</t>
@@ -370,22 +379,22 @@
     <t>四、净利润</t>
   </si>
   <si>
-    <t>宜兴度假村项目租赁项目（华东分）预算执行分析（2026年07月）</t>
+    <t>宜兴度假村项目租赁项目（华东分）预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>江苏泰州销售配餐项目_合并预算执行分析（2026年07月）</t>
+    <t>江苏泰州销售配餐项目_合并预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>上年因ERP上线提前关账，进入6个月的收入，本年是正常入7个月收入</t>
+    <t>上年因ERP上线提前关账，进入7个月的收入，本年是正常入8个月收入</t>
   </si>
   <si>
-    <t>7月新签合同额减少使收入减少</t>
+    <t>8月新签合同额减少使收入减少</t>
   </si>
   <si>
-    <t>因目前甲方接待桌餐标准及接待次数提升，原200-300一桌的便饭现需500-600一桌。原一个月3次左右，现一个月多时可达6-7次。致使今年较去年同期食材采购增加3.21万元，已进行相关费用把控，并统计餐费次数，达一定次数后与甲方沟通争取补贴。</t>
+    <t>正常经营需缴纳的税款</t>
   </si>
   <si>
-    <t>本年预算基数以项目合同测算表为基数，实际经营过程中目前存在使用退休返聘人员等情况，致使人工成本收入未完全按照测算表进度推进，若后续业主方要求更换人员，结余费用需进行使用，如替换缴纳社保人员。及此项目（高温、劳保、体检）三项费用，预算时为全年每月均摊，实际上半年未发生，三项费用5人年共计（7200元/12月*6月=3600元），上半年节约0.36万元，且上半年加班费用实际发生较预算减少，因此人工比预算节约3.13万元。</t>
+    <t>本年预算基数以项目合同测算表为基数，实际经营过程中目前存在使用退休返聘人员等情况，致使人工成本收入未完全按照测算表进度推进，若后续业主方要求更换人员，结余费用需进行使用，如替换缴纳社保人员。及此项目（高温、劳保、体检）三项费用，预算时为全年每月均摊，实际上半年未发生，三项费用5人年共计（7200元/12月*6月=3600元），上半年节约0.36万元，且上半年加班费用实际发生较预算减少，因此人工比预算节约3.49万元。</t>
   </si>
   <si>
     <t>本年为甲方举办了特色美食节活动及标准化手册等使五项费用增加</t>
@@ -394,16 +403,16 @@
     <t>上半年为甲方举办了特色美食节活动及标准化手册等使五项费用超预算，差旅费也较预算有所增加</t>
   </si>
   <si>
-    <t>江苏泰州销售配餐项目_222200150505预算执行分析（2026年07月）</t>
+    <t>江苏泰州销售配餐项目_222200150505预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>江苏泰州销售配餐项目_222200150609预算执行分析（2026年07月）</t>
+    <t>江苏泰州销售配餐项目_222200150609预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>江苏苏州销售分公司劳务输出_合并预算执行分析（2026年07月）</t>
+    <t>江苏苏州销售分公司劳务输出_合并预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>上年因ERP上线提前关账，进了6个月的收入，本年是正常入7个月收入</t>
+    <t>上年因ERP上线提前关账，进了7个月的收入，本年是正常入8个月收入</t>
   </si>
   <si>
     <t>收入比预算增加主要是加班工资增加及新增了补充协议使收入增加。</t>
@@ -418,13 +427,13 @@
     <t>差旅手续费等</t>
   </si>
   <si>
-    <t>江苏苏州销售分公司劳务输出_222200150521预算执行分析（2026年07月）</t>
+    <t>江苏苏州销售分公司劳务输出_222200150521预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>江苏苏州销售分公司劳务输出_SH3B25Z077预算执行分析（2026年07月）</t>
+    <t>江苏苏州销售分公司劳务输出_SH3B25Z077预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>中油锡山石油有限公司配餐项目_合并预算执行分析（2026年07月）</t>
+    <t>中油锡山石油有限公司配餐项目_合并预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>上年2月此项目合同结束，因此同比收入增加</t>
@@ -436,37 +445,37 @@
     <t>正常经营缴税</t>
   </si>
   <si>
-    <t>2025年7月签订合同时减少了1名员工，人工成本同比减少主要是2025年2月原合同结束后解聘了一名员工支付赔偿金4万元。</t>
+    <t>2025年7月签订合同时减少了1名员工，人工成本同比减少主要是2025年2月原合同结束后解聘了一名员工支付赔偿金4万元。2025年7月续签合同</t>
   </si>
   <si>
-    <t>本年预算基数以项目合同测算表为基数，实际经营过程中目前存在使用退休返聘人员等情况，致使人工成本收入未完全按照测算表进度推进，若后续业主方要求更换人员，结余费用需进行使用，如替换缴纳社保人员。及此项目（高温、劳保、体检）三项费用，预算时为全年每月均摊，实际上半年未发生，三项费用2人年共计（4200元/12月*6月=2100元），上半年节约0.21万元，本年实际发放福利0.1万元，因人工成本本年实际人工节约0.75万元。</t>
+    <t>本年预算基数以项目合同测算表为基数，实际经营过程中目前存在使用退休返聘人员等情况，致使人工成本收入未完全按照测算表进度推进，若后续业主方要求更换人员，结余费用需进行使用，如替换缴纳社保人员。及此项目（高温、劳保、体检）三项费用，预算时为全年每月均摊，实际上半年未发生，三项费用2人年共计（4200元/12月*6月=2100元），上半年节约0.21万元，本年实际发放福利0.1万元，因人工成本本年实际人工节约0.79万元。</t>
   </si>
   <si>
     <t>本年制作了管理手册</t>
   </si>
   <si>
-    <t>中油锡山石油有限公司配餐项目_222200150523预算执行分析（2026年07月）</t>
+    <t>中油锡山石油有限公司配餐项目_222200150523预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>中油锡山石油有限公司配餐项目_SH3B25Z075预算执行分析（2026年07月）</t>
+    <t>中油锡山石油有限公司配餐项目_SH3B25Z075预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>江苏太仓燃气公司配餐项目预算执行分析（2026年07月）</t>
+    <t>江苏太仓燃气公司配餐项目预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>此项目为含食材项目，服务费为人工部分的百分之十，人工成本部分甲方固定支付，餐费为月累计实际每日人数据实结算，业主方存在休假人员致使实际就餐人数未达预算，遂餐费部分收入比预算减少0.02万元，</t>
   </si>
   <si>
-    <t>因用餐人数减少使食材成本比预算节约0.75万元。</t>
+    <t>因用餐人数减少使食材成本比预算节约0.8万元。</t>
   </si>
   <si>
-    <t>实际经营过程中目前存在使用退休返聘人员等情况，致使人工成本收入未完全按照测算表进度推进，若后续业主方要求更换人员，结余费用需进行使用，如替换缴纳社保人员。因2025年春节在1月，福利因此在2024年12月已进账；2026年福利0.16万元在1月进账且社平基数调整，致使用工成本增加，因此同比增加0.21万元。及此项目（高温、劳保、体检）三项费用，预算时为全年每月均摊，实际上半年未发生，三项费用两人年共计（5320元/12月*6月=2660元），本年人工成本比预算减少0.34万元</t>
+    <t>实际经营过程中目前存在使用退休返聘人员等情况，致使人工成本收入未完全按照测算表进度推进，若后续业主方要求更换人员，结余费用需进行使用，如替换缴纳社保人员。因2025年春节在1月，福利因此在2024年12月已进账；2026年福利0.16万元在1月进账且社平基数调整，致使用工成本增加，因此同比增加0.21万元。及此项目（高温、劳保、体检）三项费用，预算时为全年每月均摊，实际上半年未发生，三项费用两人年共计（5320元/12月*6月=2660元），本年人工成本比预算减少0.4万元</t>
   </si>
   <si>
     <t>本年发生油烟机清洗费</t>
   </si>
   <si>
-    <t>马山檀溪1号温特莱酒店租赁项目预算执行分析（2026年07月）</t>
+    <t>马山檀溪1号温特莱酒店租赁项目预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>收入未完成预算主要是本年未进收入，</t>
@@ -481,13 +490,19 @@
     <t>折旧的减少是由于去年有提足折旧的资产。</t>
   </si>
   <si>
-    <t>荣巷门面房租赁项目预算执行分析（2026年07月）</t>
+    <t>按进度预算本月应为129万，实际本年发生113万元，折旧的减少是由于去年有提足折旧的资产</t>
   </si>
   <si>
-    <t>荣巷2025年全部出租，因此同比增加1.09万收入,</t>
+    <t>信用减值损失的增加是因为本年有353万应收账款账龄超过1年，信用减值计提了85.5万。</t>
   </si>
   <si>
-    <t>2025年底有租户提出合同结束后退租，2026年1月又全部出租完成，因此比预算增加3.88万元收入</t>
+    <t>荣巷门面房租赁项目预算执行分析（2026年08月）</t>
+  </si>
+  <si>
+    <t>荣巷2025年全部出租，因此同比增加0.9万收入,</t>
+  </si>
+  <si>
+    <t>2025年底有租户提出合同结束后退租，2026年1月又全部出租完成，因此比预算增加4.24万元收入</t>
   </si>
   <si>
     <t>2025年初因退租增加房屋维修费1.83万元，造成同比维修费减少1.83万元。</t>
@@ -499,7 +514,7 @@
     <t>预算上有空租3间，本年实际全部出租后租金上涨，使从租计征的房产税增加</t>
   </si>
   <si>
-    <t>无锡酒店商品销售项目预算执行分析（2026年07月）</t>
+    <t>无锡酒店商品销售项目预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>上半年完成杨梅销售152筐，创收2.3万元；端午粽子78盒，创收0.9万元；开展消费帮扶采购4.6万元。</t>
@@ -508,7 +523,7 @@
     <t>商品销售未达预期</t>
   </si>
   <si>
-    <t>荣巷门面房能源转售项目预算执行分析（2026年07月）</t>
+    <t>荣巷门面房能源转售项目预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>年初一间门面房退租重新招租，使转售水电的收入成本有变动</t>
@@ -517,16 +532,19 @@
     <t>门面房全部出租，能源转售项目原则上无利润。</t>
   </si>
   <si>
-    <t>天然气连云港销售分公司配餐项目_合并预算执行分析（2026年07月）</t>
+    <t>天然气连云港销售分公司配餐项目_合并预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>上年同期有加班费，合同于6月14日转入常州后，按收入配比原则进了半个月收入，综上同比收入减少0.91万元</t>
+    <t>上年同期有加班费，合同于6月14日转入常州后，按收入配比原则进了半个月收入，综上同比收入减少2.8万元</t>
   </si>
   <si>
     <t>合同转入常州后，无锡本月无收入，常州按合同时间6月进了半个月的收入</t>
   </si>
   <si>
     <t>正常经营缴纳</t>
+  </si>
+  <si>
+    <t>上年8月转为劳务外包</t>
   </si>
   <si>
     <t>但有6月1日-14日包含节日福利在内的人工成本0.67万元，且本年应业主方要求给予项目厨师两人共计0.99万元奖金，常州项目部支付全月的社保及半月的工资。</t>
@@ -538,34 +556,31 @@
     <t>本年差旅费比预算增加</t>
   </si>
   <si>
-    <t>天然气连云港销售分公司配餐项目_222200150607预算执行分析（2026年07月）</t>
+    <t>天然气连云港销售分公司配餐项目_222200150607预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>天然气连云港销售分公司配餐项目_SH3626Z001预算执行分析（2026年07月）</t>
+    <t>天然气连云港销售分公司配餐项目_SH3626Z001预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>无锡润滑脂配餐项目预算执行分析（2026年07月）</t>
+    <t>无锡润滑脂配餐项目预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>本年新签合同减少了一名管理人员，使合同金额减少1.62万元，上年同期加班费同比减少0.2万。</t>
+    <t>本年新签合同减少了一名管理人员，使合同金额减少3.24万元，上年同期加班费同比减少0.69万。</t>
   </si>
   <si>
-    <t>本年新签合同减少了一名管理人员，使月收入额减少1.62万元，本年加班费0.08万元</t>
+    <t>一季度为业主方举办了特色活动产生人工成本同比增加0.48万元</t>
   </si>
   <si>
-    <t>一季度为业主方举办了特色活动产生人工成本同比增加0.4万元</t>
-  </si>
-  <si>
-    <t>本年预算基数以项目合同测算表为基数，实际经营过程中目前存在使用退休返聘人员等情况，致使人工成本收入未完全按照测算表进度推进，若后续业主方要求更换人员，结余费用需进行使用，如替换缴纳社保人员。及此项目（高温、劳保、体检）三项费用，预算时为全年每月均摊，实际上半年未发生，三项费用2人年共计（4800元/12月*6月=2400元），上半年节约0.24万元，本年实际发放福利费0.13万元，且上半年加班费用因业主方领导班子即将调整，实际发生较预算减少，一季度为业主方举办了特色活动产生人工成本0.13万元，遂人工成本比预算减少1.25万元</t>
+    <t>本年预算基数以项目合同测算表为基数，实际经营过程中目前存在使用退休返聘人员等情况，致使人工成本收入未完全按照测算表进度推进，若后续业主方要求更换人员，结余费用需进行使用，如替换缴纳社保人员。及此项目（高温、劳保、体检）三项费用，预算时为全年每月均摊，实际上半年未发生，三项费用2人年共计（4800元/12月*6月=2400元），截至8月节约0.24万元，本年实际发放福利费0.13万元，且加班费用因业主方领导班子即将调整，实际发生较预算减少，一季度为业主方举办了特色活动产生人工成本0.13万元，遂人工成本比预算减少1.37万元</t>
   </si>
   <si>
     <t>上半年制作了管理手册</t>
   </si>
   <si>
-    <t>无锡销售配餐项目_合并预算执行分析（2026年07月）</t>
+    <t>无锡销售配餐项目_合并预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>收入同比减少69.06万元主要是去年续签合同时取消了加油站的服务项目。</t>
+    <t>收入同比减少80.17万元主要是去年续签合同时取消了加油站的服务项目。</t>
   </si>
   <si>
     <t>按合同分月四舍五入后的差异</t>
@@ -574,37 +589,37 @@
     <t>合同内容减少使人工成本减少</t>
   </si>
   <si>
-    <t>本年预算基数以项目合同测算表为基数，实际经营过程中目前存在使用退休返聘人员等情况，致使人工成本收入未完全按照测算表进度推进，若后续业主方要求更换人员，结余费用需进行使用，如替换缴纳社保人员。及此项目（高温、劳保、体检）三项费用，预算时为全年每月均摊，实际上半年未发生，三项费用五人年共计（10500元/12月*6月=5250元），上半年节约0.53万元，本年实际发放福利费0.2万元，且上半年加班费用实际发生较预算减少，遂项目人工成本上比预算节约1.85万元，</t>
+    <t>本年预算基数以项目合同测算表为基数，实际经营过程中目前存在使用退休返聘人员等情况，致使人工成本收入未完全按照测算表进度推进，若后续业主方要求更换人员，结余费用需进行使用，如替换缴纳社保人员。及此项目（高温、劳保、体检）三项费用，预算时为全年每月均摊，实际上半年未发生，三项费用五人年共计（10500元/12月*6月=5250元），上半年节约0.53万元，本年实际发放福利费0.2万元，且上半年加班费用实际发生较预算减少，遂项目人工成本上比预算节约1.41万元，</t>
   </si>
   <si>
     <t>上年有绿植的费用，上年合同到期后取消了绿植的费用</t>
   </si>
   <si>
-    <t>因属于先服务再结算因此比预算增加0.21万元的信用减值损失，</t>
+    <t>因属于先服务再结算，上年同期该项目仍在无锡核算，因此有计提</t>
   </si>
   <si>
-    <t>无锡销售配餐项目_222200150608预算执行分析（2026年07月）</t>
+    <t>无锡销售配餐项目_222200150608预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>无锡销售配餐项目_SH3626Z002预算执行分析（2026年07月）</t>
+    <t>无锡销售配餐项目_SH3626Z002预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>江苏苏州销售分公司江乾站配餐项目_合并预算执行分析（2026年07月）</t>
+    <t>江苏苏州销售分公司江乾站配餐项目_合并预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>主要原因为华兴劳务公司按照应收1.35%缴纳残保金</t>
   </si>
   <si>
-    <t>本年预算基数以项目合同测算表为基数，实际经营过程中目前存在使用退休返聘人员等情况，致使人工成本收入未完全按照测算表进度推进，若后续业主方要求更换人员，结余费用需进行使用，如替换缴纳社保人员。及此项目（高温、劳保、体检）三项费用，预算时为全年每月均摊，实际上半年未发生，三项费用3人年共计（4770元/12月*6月=2384元），上半年节省0.12万元，本年实际发生福利费0.39万元，华兴劳务公司按照应收1.35%缴纳残保金。上年2月发生工服采购款0.05万元。遂人工成本同比增加0.2万元，比预算减少0.34万元，</t>
+    <t>本年预算基数以项目合同测算表为基数，实际经营过程中目前存在使用退休返聘人员等情况，致使人工成本收入未完全按照测算表进度推进，若后续业主方要求更换人员，结余费用需进行使用，如替换缴纳社保人员。及此项目（高温、劳保、体检）三项费用，预算时为全年每月均摊，实际上半年未发生，三项费用3人年共计（4770元/12月*6月=2384元），上半年节省0.12万元，本年实际发生福利费0.39万元，华兴劳务公司按照应收1.35%缴纳残保金。上年2月发生工服采购款0.05万元。遂人工成本同比增加0.2万元，比预算减少0.5万元，</t>
   </si>
   <si>
-    <t>江苏苏州销售分公司江乾站配餐项目_222200150912预算执行分析（2026年07月）</t>
+    <t>江苏苏州销售分公司江乾站配餐项目_222200150912预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>江苏苏州销售分公司江乾站配餐项目_SH3B25Z079预算执行分析（2026年07月）</t>
+    <t>江苏苏州销售分公司江乾站配餐项目_SH3B25Z079预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>苏州销售太仓实训基地预算执行分析（2026年07月）</t>
+    <t>苏州销售太仓实训基地预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>2025年11月新增项目</t>
@@ -616,7 +631,7 @@
     <t>正常经营纳税</t>
   </si>
   <si>
-    <t>本年预算基数以项目合同测算表为基数，实际经营过程中目前存在使用退休返聘人员等情况，致使人工成本收入未完全按照测算表进度推进，若后续业主方要求更换人员，结余费用需进行使用，如替换缴纳社保人员。及此项目（高温、劳保、体检）三项费用，预算时为全年每月均摊，实际上半年未发生，三项费用4人年共计（9600元/12月*6月=4800元），上半年节省0.48万元，本年发放节日福利0.6万元，且上半年加班费用实际发生较预算减少，因此人工节约2.91万元。</t>
+    <t>本年预算基数以项目合同测算表为基数，实际经营过程中目前存在使用退休返聘人员等情况，致使人工成本收入未完全按照测算表进度推进，若后续业主方要求更换人员，结余费用需进行使用，如替换缴纳社保人员。及此项目（高温、劳保、体检）三项费用，预算时为全年每月均摊，实际上半年未发生，三项费用4人年共计（9600元/12月*6月=4800元），上半年节省0.48万元，本年发放节日福利0.6万元，且上半年加班费用实际发生较预算减少，因此人工节约3.53万元。</t>
   </si>
   <si>
     <t>本年有预算外的差旅及管理手册的支出使五项费用增加0.06万元</t>
@@ -1124,7 +1139,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -1474,7 +1489,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -1492,7 +1507,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -1510,7 +1525,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -1528,7 +1543,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -1546,7 +1561,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -1564,7 +1579,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -1582,7 +1597,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -1600,7 +1615,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -1618,7 +1633,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -1636,7 +1651,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -1654,7 +1669,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -1672,7 +1687,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -1690,7 +1705,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -1708,7 +1723,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -1726,7 +1741,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -1744,7 +1759,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -1762,7 +1777,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -1780,7 +1795,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -1798,7 +1813,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -1816,7 +1831,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -1834,7 +1849,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -1852,7 +1867,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -1889,7 +1904,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -1959,11 +1974,11 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
@@ -2179,11 +2194,11 @@
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="12" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="H15" s="11"/>
       <c r="I15" s="12" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
@@ -2209,7 +2224,7 @@
       <c r="M16" s="11"/>
       <c r="N16" s="11"/>
     </row>
-    <row r="17" ht="112.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" ht="131.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>63</v>
       </c>
@@ -2219,7 +2234,7 @@
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
       <c r="G17" s="12" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="H17" s="11"/>
       <c r="I17" s="12"/>
@@ -2241,7 +2256,7 @@
       <c r="G18" s="12"/>
       <c r="H18" s="11"/>
       <c r="I18" s="12" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
@@ -2251,7 +2266,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -2269,7 +2284,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -2287,7 +2302,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -2305,7 +2320,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -2323,7 +2338,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -2331,7 +2346,7 @@
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
       <c r="G23" s="12" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="H23" s="11"/>
       <c r="I23" s="12"/>
@@ -2343,7 +2358,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -2361,7 +2376,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -2379,7 +2394,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -2397,7 +2412,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -2415,7 +2430,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -2433,7 +2448,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -2451,7 +2466,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -2469,7 +2484,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -2487,7 +2502,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -2505,7 +2520,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -2523,7 +2538,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -2541,7 +2556,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -2559,7 +2574,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -2577,7 +2592,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -2595,7 +2610,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -2613,7 +2628,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -2631,7 +2646,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -2668,7 +2683,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -3018,7 +3033,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -3036,7 +3051,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -3054,7 +3069,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -3072,7 +3087,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -3090,7 +3105,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -3108,7 +3123,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -3126,7 +3141,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -3144,7 +3159,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -3162,7 +3177,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -3180,7 +3195,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -3198,7 +3213,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -3216,7 +3231,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -3234,7 +3249,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -3252,7 +3267,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -3270,7 +3285,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -3288,7 +3303,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -3306,7 +3321,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -3324,7 +3339,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -3342,7 +3357,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -3360,7 +3375,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -3378,7 +3393,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -3396,7 +3411,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -3433,7 +3448,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -3783,7 +3798,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -3801,7 +3816,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -3819,7 +3834,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -3837,7 +3852,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -3855,7 +3870,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -3873,7 +3888,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -3891,7 +3906,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -3909,7 +3924,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -3927,7 +3942,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -3945,7 +3960,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -3963,7 +3978,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -3981,7 +3996,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -3999,7 +4014,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -4017,7 +4032,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -4035,7 +4050,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -4053,7 +4068,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -4071,7 +4086,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -4089,7 +4104,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -4107,7 +4122,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -4125,7 +4140,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -4143,7 +4158,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -4161,7 +4176,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -4198,7 +4213,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -4268,11 +4283,11 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
@@ -4294,7 +4309,7 @@
       </c>
       <c r="H4" s="11"/>
       <c r="I4" s="12" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="J4" s="11"/>
       <c r="K4" s="11"/>
@@ -4492,11 +4507,11 @@
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="12" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="H15" s="11"/>
       <c r="I15" s="12" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
@@ -4554,7 +4569,7 @@
       <c r="G18" s="12"/>
       <c r="H18" s="11"/>
       <c r="I18" s="12" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
@@ -4564,7 +4579,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -4582,7 +4597,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -4600,7 +4615,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -4618,7 +4633,7 @@
     </row>
     <row r="22" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -4628,7 +4643,7 @@
       <c r="G22" s="12"/>
       <c r="H22" s="11"/>
       <c r="I22" s="12" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="J22" s="11"/>
       <c r="K22" s="11"/>
@@ -4638,7 +4653,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -4656,7 +4671,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -4674,7 +4689,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -4692,7 +4707,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -4710,7 +4725,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -4728,7 +4743,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -4746,7 +4761,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -4764,7 +4779,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -4782,7 +4797,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -4800,7 +4815,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -4818,7 +4833,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -4836,7 +4851,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -4854,7 +4869,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -4872,7 +4887,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -4890,7 +4905,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -4908,7 +4923,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -4926,7 +4941,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -4944,7 +4959,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -4981,7 +4996,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -5051,11 +5066,11 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
@@ -5073,11 +5088,11 @@
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
       <c r="G4" s="12" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="H4" s="11"/>
       <c r="I4" s="12" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="J4" s="11"/>
       <c r="K4" s="11"/>
@@ -5275,11 +5290,11 @@
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="12" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="H15" s="11"/>
       <c r="I15" s="12" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
@@ -5347,7 +5362,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -5365,7 +5380,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -5383,7 +5398,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -5401,7 +5416,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -5419,7 +5434,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -5437,7 +5452,7 @@
     </row>
     <row r="24" ht="75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -5445,11 +5460,11 @@
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="12" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H24" s="11"/>
       <c r="I24" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J24" s="11"/>
       <c r="K24" s="11"/>
@@ -5457,9 +5472,9 @@
       <c r="M24" s="11"/>
       <c r="N24" s="11"/>
     </row>
-    <row r="25" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" ht="93.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -5467,11 +5482,11 @@
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="12" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="H25" s="11"/>
       <c r="I25" s="12" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="J25" s="11"/>
       <c r="K25" s="11"/>
@@ -5481,7 +5496,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -5499,7 +5514,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -5517,7 +5532,7 @@
     </row>
     <row r="28" ht="93.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -5525,11 +5540,11 @@
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
       <c r="G28" s="12" t="s">
-        <v>87</v>
+        <v>143</v>
       </c>
       <c r="H28" s="11"/>
       <c r="I28" s="12" t="s">
-        <v>87</v>
+        <v>143</v>
       </c>
       <c r="J28" s="11"/>
       <c r="K28" s="11"/>
@@ -5539,7 +5554,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -5557,7 +5572,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -5575,7 +5590,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -5593,7 +5608,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -5611,7 +5626,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -5629,7 +5644,7 @@
     </row>
     <row r="34" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -5637,7 +5652,7 @@
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="12" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="H34" s="11"/>
       <c r="I34" s="12"/>
@@ -5649,7 +5664,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -5667,7 +5682,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -5685,7 +5700,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -5703,7 +5718,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -5721,7 +5736,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -5739,7 +5754,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -5776,7 +5791,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -5846,11 +5861,11 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
@@ -6130,7 +6145,7 @@
     </row>
     <row r="19" ht="75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -6138,7 +6153,7 @@
       <c r="E19" s="11"/>
       <c r="F19" s="11"/>
       <c r="G19" s="12" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="H19" s="11"/>
       <c r="I19" s="12"/>
@@ -6150,7 +6165,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -6168,7 +6183,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -6186,7 +6201,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -6204,7 +6219,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -6222,7 +6237,7 @@
     </row>
     <row r="24" ht="75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -6230,11 +6245,11 @@
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="12" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="H24" s="11"/>
       <c r="I24" s="12" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J24" s="11"/>
       <c r="K24" s="11"/>
@@ -6244,7 +6259,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -6262,7 +6277,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -6280,7 +6295,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -6298,7 +6313,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -6316,7 +6331,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -6334,7 +6349,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -6352,7 +6367,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -6370,7 +6385,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -6388,7 +6403,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -6406,7 +6421,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -6424,7 +6439,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -6442,7 +6457,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -6460,7 +6475,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -6478,7 +6493,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -6496,7 +6511,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -6514,7 +6529,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -6551,7 +6566,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -6621,11 +6636,11 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
@@ -6905,7 +6920,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -6923,7 +6938,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -6941,7 +6956,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -6959,7 +6974,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -6977,7 +6992,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -6995,7 +7010,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -7013,7 +7028,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -7031,7 +7046,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -7049,7 +7064,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -7067,7 +7082,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -7085,7 +7100,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -7103,7 +7118,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -7121,7 +7136,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -7139,7 +7154,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -7157,7 +7172,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -7175,7 +7190,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -7193,7 +7208,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -7211,7 +7226,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -7229,7 +7244,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -7247,7 +7262,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -7265,7 +7280,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -7283,7 +7298,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -7320,7 +7335,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -7390,11 +7405,11 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
@@ -7674,7 +7689,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -7692,7 +7707,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -7710,7 +7725,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -7728,7 +7743,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -7746,7 +7761,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -7764,7 +7779,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -7782,7 +7797,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -7800,7 +7815,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -7818,7 +7833,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -7836,7 +7851,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -7854,7 +7869,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -7872,7 +7887,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -7890,7 +7905,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -7908,7 +7923,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -7926,7 +7941,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -7944,7 +7959,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -7962,7 +7977,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -7980,7 +7995,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -7998,7 +8013,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -8016,7 +8031,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -8034,7 +8049,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -8052,7 +8067,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -8089,7 +8104,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -8159,11 +8174,11 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
@@ -8379,11 +8394,11 @@
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="12" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="H15" s="11"/>
       <c r="I15" s="12" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
@@ -8409,7 +8424,7 @@
       <c r="M16" s="11"/>
       <c r="N16" s="11"/>
     </row>
-    <row r="17" ht="150" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>63</v>
       </c>
@@ -8418,8 +8433,8 @@
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="12" t="s">
-        <v>155</v>
+      <c r="G17" t="s">
+        <v>160</v>
       </c>
       <c r="H17" s="11"/>
       <c r="I17" s="12"/>
@@ -8429,7 +8444,7 @@
       <c r="M17" s="11"/>
       <c r="N17" s="11"/>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" ht="150" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>66</v>
       </c>
@@ -8438,7 +8453,9 @@
       <c r="D18" s="11"/>
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
-      <c r="G18" s="12"/>
+      <c r="G18" s="12" t="s">
+        <v>161</v>
+      </c>
       <c r="H18" s="11"/>
       <c r="I18" s="12"/>
       <c r="J18" s="11"/>
@@ -8449,7 +8466,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -8467,7 +8484,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -8485,7 +8502,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -8503,7 +8520,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -8521,7 +8538,7 @@
     </row>
     <row r="23" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -8529,11 +8546,11 @@
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
       <c r="G23" s="12" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="H23" s="11"/>
       <c r="I23" s="12" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="J23" s="11"/>
       <c r="K23" s="11"/>
@@ -8543,7 +8560,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -8561,7 +8578,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -8579,7 +8596,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -8597,7 +8614,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -8615,7 +8632,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -8633,7 +8650,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -8651,7 +8668,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -8669,7 +8686,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -8687,7 +8704,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -8705,7 +8722,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -8723,7 +8740,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -8741,7 +8758,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -8759,7 +8776,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -8777,7 +8794,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -8795,7 +8812,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -8813,7 +8830,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -8831,7 +8848,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -9175,7 +9192,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -9525,7 +9542,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -9543,7 +9560,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -9561,7 +9578,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -9579,7 +9596,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -9597,7 +9614,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -9615,7 +9632,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -9633,7 +9650,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -9651,7 +9668,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -9669,7 +9686,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -9687,7 +9704,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -9705,7 +9722,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -9723,7 +9740,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -9741,7 +9758,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -9759,7 +9776,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -9777,7 +9794,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -9795,7 +9812,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -9813,7 +9830,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -9831,7 +9848,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -9849,7 +9866,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -9867,7 +9884,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -9885,7 +9902,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -9903,7 +9920,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -9940,7 +9957,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -10290,7 +10307,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -10308,7 +10325,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -10326,7 +10343,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -10344,7 +10361,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -10362,7 +10379,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -10380,7 +10397,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -10398,7 +10415,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -10416,7 +10433,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -10434,7 +10451,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -10452,7 +10469,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -10470,7 +10487,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -10488,7 +10505,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -10506,7 +10523,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -10524,7 +10541,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -10542,7 +10559,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -10560,7 +10577,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -10578,7 +10595,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -10596,7 +10613,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -10614,7 +10631,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -10632,7 +10649,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -10650,7 +10667,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -10668,7 +10685,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -10705,7 +10722,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -10775,11 +10792,11 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
@@ -10995,11 +11012,11 @@
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="12" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="H15" s="11"/>
       <c r="I15" s="12" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
@@ -11025,7 +11042,7 @@
       <c r="M16" s="11"/>
       <c r="N16" s="11"/>
     </row>
-    <row r="17" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>63</v>
       </c>
@@ -11034,9 +11051,6 @@
       <c r="D17" s="11"/>
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="12" t="s">
-        <v>163</v>
-      </c>
       <c r="H17" s="11"/>
       <c r="I17" s="12"/>
       <c r="J17" s="11"/>
@@ -11054,10 +11068,12 @@
       <c r="D18" s="11"/>
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
-      <c r="G18" s="12"/>
+      <c r="G18" s="12" t="s">
+        <v>168</v>
+      </c>
       <c r="H18" s="11"/>
       <c r="I18" s="12" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
@@ -11067,7 +11083,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -11085,7 +11101,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -11103,7 +11119,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -11121,7 +11137,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -11139,7 +11155,7 @@
     </row>
     <row r="23" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -11147,7 +11163,7 @@
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
       <c r="G23" s="12" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="H23" s="11"/>
       <c r="I23" s="12"/>
@@ -11159,7 +11175,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -11177,7 +11193,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -11195,7 +11211,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -11213,7 +11229,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -11231,7 +11247,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -11249,7 +11265,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -11267,7 +11283,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -11285,7 +11301,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -11303,7 +11319,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -11321,7 +11337,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -11339,7 +11355,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -11357,7 +11373,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -11375,7 +11391,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -11393,7 +11409,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -11411,7 +11427,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -11429,7 +11445,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -11447,7 +11463,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -11484,7 +11500,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -11554,11 +11570,11 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
@@ -11774,11 +11790,11 @@
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="12" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="H15" s="11"/>
       <c r="I15" s="12" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
@@ -11814,7 +11830,7 @@
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
       <c r="G17" s="12" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="H17" s="11"/>
       <c r="I17" s="12"/>
@@ -11836,7 +11852,7 @@
       <c r="G18" s="12"/>
       <c r="H18" s="11"/>
       <c r="I18" s="12" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
@@ -11846,7 +11862,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -11864,7 +11880,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -11882,7 +11898,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -11900,7 +11916,7 @@
     </row>
     <row r="22" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -11908,7 +11924,7 @@
       <c r="E22" s="11"/>
       <c r="F22" s="11"/>
       <c r="G22" s="12" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="H22" s="11"/>
       <c r="I22" s="12"/>
@@ -11920,7 +11936,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -11938,7 +11954,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -11956,7 +11972,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -11974,7 +11990,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -11992,7 +12008,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -12008,20 +12024,20 @@
       <c r="M27" s="11"/>
       <c r="N27" s="11"/>
     </row>
-    <row r="28" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" ht="75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
       <c r="D28" s="11"/>
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
-      <c r="G28" s="12"/>
+      <c r="G28" s="12" t="s">
+        <v>177</v>
+      </c>
       <c r="H28" s="11"/>
-      <c r="I28" s="12" t="s">
-        <v>172</v>
-      </c>
+      <c r="I28" s="12"/>
       <c r="J28" s="11"/>
       <c r="K28" s="11"/>
       <c r="L28" s="11"/>
@@ -12030,7 +12046,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -12048,7 +12064,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -12066,7 +12082,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -12084,7 +12100,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -12102,7 +12118,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -12120,7 +12136,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -12138,7 +12154,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -12156,7 +12172,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -12174,7 +12190,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -12192,7 +12208,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -12210,7 +12226,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -12228,7 +12244,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -12265,7 +12281,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -12615,7 +12631,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -12633,7 +12649,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -12651,7 +12667,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -12669,7 +12685,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -12687,7 +12703,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -12705,7 +12721,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -12723,7 +12739,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -12741,7 +12757,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -12759,7 +12775,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -12777,7 +12793,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -12795,7 +12811,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -12813,7 +12829,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -12831,7 +12847,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -12849,7 +12865,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -12867,7 +12883,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -12885,7 +12901,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -12903,7 +12919,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -12921,7 +12937,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -12939,7 +12955,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -12957,7 +12973,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -12975,7 +12991,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -12993,7 +13009,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -13030,7 +13046,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -13380,7 +13396,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -13398,7 +13414,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -13416,7 +13432,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -13434,7 +13450,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -13452,7 +13468,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -13470,7 +13486,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -13488,7 +13504,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -13506,7 +13522,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -13524,7 +13540,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -13542,7 +13558,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -13560,7 +13576,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -13578,7 +13594,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -13596,7 +13612,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -13614,7 +13630,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -13632,7 +13648,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -13650,7 +13666,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -13668,7 +13684,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -13686,7 +13702,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -13704,7 +13720,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -13722,7 +13738,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -13740,7 +13756,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -13758,7 +13774,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -13795,7 +13811,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -14081,7 +14097,7 @@
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="12" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="H15" s="11"/>
       <c r="I15" s="12"/>
@@ -14119,7 +14135,7 @@
       <c r="E17" s="11"/>
       <c r="F17" s="11"/>
       <c r="G17" s="12" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="H17" s="11"/>
       <c r="I17" s="12"/>
@@ -14141,7 +14157,7 @@
       <c r="G18" s="12"/>
       <c r="H18" s="11"/>
       <c r="I18" s="12" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
@@ -14151,7 +14167,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -14169,7 +14185,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -14187,7 +14203,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -14205,7 +14221,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -14223,7 +14239,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -14231,7 +14247,7 @@
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
       <c r="G23" s="12" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="H23" s="11"/>
       <c r="I23" s="12"/>
@@ -14243,7 +14259,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -14261,7 +14277,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -14279,7 +14295,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -14297,7 +14313,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -14315,7 +14331,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -14333,7 +14349,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -14351,7 +14367,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -14369,7 +14385,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -14387,7 +14403,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -14405,7 +14421,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -14423,7 +14439,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -14441,7 +14457,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -14459,7 +14475,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -14477,7 +14493,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -14495,7 +14511,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -14513,7 +14529,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -14531,7 +14547,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -14568,7 +14584,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -14918,7 +14934,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -14936,7 +14952,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -14954,7 +14970,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -14972,7 +14988,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -14990,7 +15006,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -15008,7 +15024,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -15026,7 +15042,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -15044,7 +15060,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -15062,7 +15078,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -15080,7 +15096,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -15098,7 +15114,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -15116,7 +15132,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -15134,7 +15150,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -15152,7 +15168,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -15170,7 +15186,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -15188,7 +15204,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -15206,7 +15222,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -15224,7 +15240,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -15242,7 +15258,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -15260,7 +15276,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -15278,7 +15294,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -15296,7 +15312,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -15333,7 +15349,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -15683,7 +15699,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -15701,7 +15717,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -15719,7 +15735,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -15737,7 +15753,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -15755,7 +15771,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -15773,7 +15789,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -15791,7 +15807,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -15809,7 +15825,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -15827,7 +15843,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -15845,7 +15861,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -15863,7 +15879,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -15881,7 +15897,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -15899,7 +15915,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -15917,7 +15933,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -15935,7 +15951,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -15953,7 +15969,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -15971,7 +15987,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -15989,7 +16005,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -16007,7 +16023,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -16025,7 +16041,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -16043,7 +16059,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -16061,7 +16077,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -16098,7 +16114,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -16168,11 +16184,11 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
@@ -16388,11 +16404,11 @@
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="12" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="H15" s="11"/>
       <c r="I15" s="12" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
@@ -16446,11 +16462,11 @@
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
       <c r="G18" s="12" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="H18" s="11"/>
       <c r="I18" s="12" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
@@ -16460,7 +16476,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -16478,7 +16494,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -16496,7 +16512,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -16514,7 +16530,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -16532,7 +16548,7 @@
     </row>
     <row r="23" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -16540,11 +16556,11 @@
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
       <c r="G23" s="12" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="H23" s="11"/>
       <c r="I23" s="12" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="J23" s="11"/>
       <c r="K23" s="11"/>
@@ -16554,7 +16570,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -16572,7 +16588,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -16590,7 +16606,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -16608,7 +16624,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -16626,7 +16642,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -16644,7 +16660,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -16662,7 +16678,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -16680,7 +16696,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -16698,7 +16714,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -16716,7 +16732,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -16734,7 +16750,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -16752,7 +16768,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -16770,7 +16786,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -16788,7 +16804,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -16806,7 +16822,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -16814,7 +16830,7 @@
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="12" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="H38" s="11"/>
       <c r="I38" s="12"/>
@@ -16826,7 +16842,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -16844,7 +16860,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -16963,7 +16979,7 @@
       <c r="M3" s="11"/>
       <c r="N3" s="11"/>
     </row>
-    <row r="4" ht="94" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" ht="75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>47</v>
       </c>
@@ -17165,7 +17181,7 @@
       <c r="M14" s="11"/>
       <c r="N14" s="11"/>
     </row>
-    <row r="15" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>60</v>
       </c>
@@ -17227,7 +17243,7 @@
       <c r="M17" s="11"/>
       <c r="N17" s="11"/>
     </row>
-    <row r="18" ht="56.25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" ht="300" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>66</v>
       </c>
@@ -17237,11 +17253,11 @@
       <c r="E18" s="11"/>
       <c r="F18" s="11"/>
       <c r="G18" s="12" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H18" s="11"/>
       <c r="I18" s="12" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
@@ -17249,9 +17265,9 @@
       <c r="M18" s="11"/>
       <c r="N18" s="11"/>
     </row>
-    <row r="19" ht="46" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -17259,11 +17275,11 @@
       <c r="E19" s="11"/>
       <c r="F19" s="11"/>
       <c r="G19" s="12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H19" s="11"/>
       <c r="I19" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J19" s="11"/>
       <c r="K19" s="11"/>
@@ -17273,7 +17289,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -17291,7 +17307,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -17309,7 +17325,7 @@
     </row>
     <row r="22" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -17317,11 +17333,11 @@
       <c r="E22" s="11"/>
       <c r="F22" s="11"/>
       <c r="G22" s="12" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H22" s="11"/>
       <c r="I22" s="12" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J22" s="11"/>
       <c r="K22" s="11"/>
@@ -17331,7 +17347,7 @@
     </row>
     <row r="23" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -17339,11 +17355,11 @@
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
       <c r="G23" s="12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H23" s="11"/>
       <c r="I23" s="12" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J23" s="11"/>
       <c r="K23" s="11"/>
@@ -17353,7 +17369,7 @@
     </row>
     <row r="24" ht="75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -17361,11 +17377,11 @@
       <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="12" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H24" s="11"/>
       <c r="I24" s="12" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J24" s="11"/>
       <c r="K24" s="11"/>
@@ -17375,7 +17391,7 @@
     </row>
     <row r="25" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -17383,11 +17399,11 @@
       <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="12" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H25" s="11"/>
       <c r="I25" s="12" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J25" s="11"/>
       <c r="K25" s="11"/>
@@ -17395,9 +17411,9 @@
       <c r="M25" s="11"/>
       <c r="N25" s="11"/>
     </row>
-    <row r="26" ht="33" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -17415,7 +17431,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -17433,7 +17449,7 @@
     </row>
     <row r="28" ht="93.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -17441,11 +17457,11 @@
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
       <c r="G28" s="12" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H28" s="11"/>
       <c r="I28" s="12" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J28" s="11"/>
       <c r="K28" s="11"/>
@@ -17455,7 +17471,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -17473,7 +17489,7 @@
     </row>
     <row r="30" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -17481,11 +17497,11 @@
       <c r="E30" s="11"/>
       <c r="F30" s="11"/>
       <c r="G30" s="12" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="H30" s="11"/>
       <c r="I30" s="12" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="J30" s="11"/>
       <c r="K30" s="11"/>
@@ -17495,7 +17511,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -17513,7 +17529,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -17531,7 +17547,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -17549,7 +17565,7 @@
     </row>
     <row r="34" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -17557,11 +17573,11 @@
       <c r="E34" s="11"/>
       <c r="F34" s="11"/>
       <c r="G34" s="12" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="H34" s="11"/>
       <c r="I34" s="12" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J34" s="11"/>
       <c r="K34" s="11"/>
@@ -17571,7 +17587,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -17589,7 +17605,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -17607,7 +17623,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -17625,7 +17641,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -17643,7 +17659,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -17661,7 +17677,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -17698,7 +17714,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -18048,7 +18064,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -18066,7 +18082,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -18084,7 +18100,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -18102,7 +18118,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -18120,7 +18136,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -18138,7 +18154,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -18156,7 +18172,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -18174,7 +18190,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -18192,7 +18208,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -18210,7 +18226,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -18228,7 +18244,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -18246,7 +18262,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -18264,7 +18280,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -18282,7 +18298,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -18300,7 +18316,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -18318,7 +18334,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -18336,7 +18352,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -18354,7 +18370,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -18372,7 +18388,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -18390,7 +18406,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -18408,7 +18424,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -18426,7 +18442,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -18463,7 +18479,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -18533,11 +18549,11 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
@@ -18545,7 +18561,7 @@
       <c r="M3" s="11"/>
       <c r="N3" s="11"/>
     </row>
-    <row r="4" ht="243.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" ht="75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>47</v>
       </c>
@@ -18558,9 +18574,7 @@
         <v>48</v>
       </c>
       <c r="H4" s="11"/>
-      <c r="I4" s="12" t="s">
-        <v>106</v>
-      </c>
+      <c r="I4" s="12"/>
       <c r="J4" s="11"/>
       <c r="K4" s="11"/>
       <c r="L4" s="11"/>
@@ -18757,7 +18771,7 @@
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="12" t="s">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="H15" s="11"/>
       <c r="I15" s="12"/>
@@ -18805,7 +18819,7 @@
       <c r="M17" s="11"/>
       <c r="N17" s="11"/>
     </row>
-    <row r="18" ht="409" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" ht="409.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>66</v>
       </c>
@@ -18819,7 +18833,7 @@
       </c>
       <c r="H18" s="11"/>
       <c r="I18" s="12" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
@@ -18829,7 +18843,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -18847,7 +18861,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -18865,7 +18879,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -18883,7 +18897,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -18901,7 +18915,7 @@
     </row>
     <row r="23" ht="93.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -18909,11 +18923,11 @@
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
       <c r="G23" s="12" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="H23" s="11"/>
       <c r="I23" s="12" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="J23" s="11"/>
       <c r="K23" s="11"/>
@@ -18923,7 +18937,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -18941,7 +18955,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -18959,7 +18973,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -18977,7 +18991,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -18995,7 +19009,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -19013,7 +19027,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -19031,7 +19045,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -19049,7 +19063,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -19067,7 +19081,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -19085,7 +19099,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -19103,7 +19117,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -19121,7 +19135,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -19139,7 +19153,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -19157,7 +19171,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -19175,7 +19189,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -19193,7 +19207,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -19211,7 +19225,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -19248,7 +19262,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -19598,7 +19612,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -19616,7 +19630,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -19634,7 +19648,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -19652,7 +19666,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -19670,7 +19684,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -19688,7 +19702,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -19706,7 +19720,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -19724,7 +19738,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -19742,7 +19756,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -19760,7 +19774,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -19778,7 +19792,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -19796,7 +19810,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -19814,7 +19828,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -19832,7 +19846,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -19850,7 +19864,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -19868,7 +19882,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -19886,7 +19900,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -19904,7 +19918,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -19922,7 +19936,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -19940,7 +19954,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -19958,7 +19972,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -19976,7 +19990,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -20013,7 +20027,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -20363,7 +20377,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -20381,7 +20395,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -20399,7 +20413,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -20417,7 +20431,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -20435,7 +20449,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -20453,7 +20467,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -20471,7 +20485,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -20489,7 +20503,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -20507,7 +20521,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -20525,7 +20539,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -20543,7 +20557,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -20561,7 +20575,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -20579,7 +20593,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -20597,7 +20611,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -20615,7 +20629,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -20633,7 +20647,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -20651,7 +20665,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -20669,7 +20683,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -20687,7 +20701,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -20705,7 +20719,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -20723,7 +20737,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -20741,7 +20755,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -20778,7 +20792,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -20848,11 +20862,11 @@
       <c r="E3" s="11"/>
       <c r="F3" s="11"/>
       <c r="G3" s="12" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="H3" s="11"/>
       <c r="I3" s="12" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="11"/>
@@ -21068,11 +21082,11 @@
       <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="12" t="s">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="H15" s="11"/>
       <c r="I15" s="12" t="s">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="J15" s="11"/>
       <c r="K15" s="11"/>
@@ -21130,7 +21144,7 @@
       <c r="G18" s="12"/>
       <c r="H18" s="11"/>
       <c r="I18" s="12" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="J18" s="11"/>
       <c r="K18" s="11"/>
@@ -21140,7 +21154,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -21158,7 +21172,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -21176,7 +21190,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -21194,7 +21208,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -21212,7 +21226,7 @@
     </row>
     <row r="23" ht="37.5" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -21220,7 +21234,7 @@
       <c r="E23" s="11"/>
       <c r="F23" s="11"/>
       <c r="G23" s="12" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="H23" s="11"/>
       <c r="I23" s="12"/>
@@ -21232,7 +21246,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -21250,7 +21264,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -21268,7 +21282,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -21276,7 +21290,7 @@
       <c r="E26" s="11"/>
       <c r="F26" s="11"/>
       <c r="G26" s="12" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H26" s="11"/>
       <c r="I26" s="12"/>
@@ -21288,7 +21302,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -21306,7 +21320,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -21324,7 +21338,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -21342,7 +21356,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -21360,7 +21374,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -21378,7 +21392,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -21396,7 +21410,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -21414,7 +21428,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -21432,7 +21446,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -21450,7 +21464,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -21468,7 +21482,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -21486,7 +21500,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -21504,7 +21518,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -21522,7 +21536,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>
@@ -21559,7 +21573,7 @@
   <sheetData>
     <row r="1" ht="41" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -21909,7 +21923,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B19" s="11"/>
       <c r="C19" s="11"/>
@@ -21927,7 +21941,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
@@ -21945,7 +21959,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B21" s="11"/>
       <c r="C21" s="11"/>
@@ -21963,7 +21977,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -21981,7 +21995,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="11"/>
@@ -21999,7 +22013,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -22017,7 +22031,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B25" s="11"/>
       <c r="C25" s="11"/>
@@ -22035,7 +22049,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -22053,7 +22067,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -22071,7 +22085,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -22089,7 +22103,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B29" s="11"/>
       <c r="C29" s="11"/>
@@ -22107,7 +22121,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -22125,7 +22139,7 @@
     </row>
     <row r="31" ht="18" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
@@ -22143,7 +22157,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="18" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -22161,7 +22175,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -22179,7 +22193,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="18" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -22197,7 +22211,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
@@ -22215,7 +22229,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B36" s="11"/>
       <c r="C36" s="11"/>
@@ -22233,7 +22247,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B37" s="11"/>
       <c r="C37" s="11"/>
@@ -22251,7 +22265,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B38" s="11"/>
       <c r="C38" s="11"/>
@@ -22269,7 +22283,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -22287,7 +22301,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="22" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B40" s="11"/>
       <c r="C40" s="11"/>

--- a/public/管理口径原因分析默认模版/无锡宜兴项目.xlsx
+++ b/public/管理口径原因分析默认模版/无锡宜兴项目.xlsx
@@ -9,32 +9,32 @@
   <sheets>
     <sheet sheetId="2" name="目录" state="visible" r:id="rId4"/>
     <sheet sheetId="3" name="合计" state="visible" r:id="rId5"/>
-    <sheet sheetId="4" name="宜兴度假村项目租赁项目（华东分）" state="visible" r:id="rId6"/>
-    <sheet sheetId="5" name="江苏泰州销售配餐项目_合并" state="visible" r:id="rId7"/>
-    <sheet sheetId="6" name="江苏泰州销售配餐项目_222200150505" state="visible" r:id="rId8"/>
-    <sheet sheetId="7" name="江苏泰州销售配餐项目_222200150609" state="visible" r:id="rId9"/>
-    <sheet sheetId="8" name="江苏苏州销售分公司劳务输出_合并" state="visible" r:id="rId10"/>
-    <sheet sheetId="9" name="江苏苏州销售分公司劳务输出_222200150521" state="visible" r:id="rId11"/>
-    <sheet sheetId="10" name="江苏苏州销售分公司劳务输出_SH3B25Z077" state="visible" r:id="rId12"/>
-    <sheet sheetId="11" name="中油锡山石油有限公司配餐项目_合并" state="visible" r:id="rId13"/>
-    <sheet sheetId="12" name="中油锡山石油有限公司配餐项目_222200150523" state="visible" r:id="rId14"/>
-    <sheet sheetId="13" name="中油锡山石油有限公司配餐项目_SH3B25Z075" state="visible" r:id="rId15"/>
-    <sheet sheetId="14" name="江苏太仓燃气公司配餐项目" state="visible" r:id="rId16"/>
-    <sheet sheetId="15" name="马山檀溪1号温特莱酒店租赁项目" state="visible" r:id="rId17"/>
-    <sheet sheetId="16" name="荣巷门面房租赁项目" state="visible" r:id="rId18"/>
-    <sheet sheetId="17" name="无锡酒店商品销售项目" state="visible" r:id="rId19"/>
-    <sheet sheetId="18" name="荣巷门面房能源转售项目" state="visible" r:id="rId20"/>
-    <sheet sheetId="19" name="天然气连云港销售分公司配餐项目_合并" state="visible" r:id="rId21"/>
-    <sheet sheetId="20" name="天然气连云港销售分公司配餐项目_222200150607" state="visible" r:id="rId22"/>
-    <sheet sheetId="21" name="天然气连云港销售分公司配餐项目_SH3626Z001" state="visible" r:id="rId23"/>
-    <sheet sheetId="22" name="无锡润滑脂配餐项目" state="visible" r:id="rId24"/>
-    <sheet sheetId="23" name="无锡销售配餐项目_合并" state="visible" r:id="rId25"/>
-    <sheet sheetId="24" name="无锡销售配餐项目_222200150608" state="visible" r:id="rId26"/>
-    <sheet sheetId="25" name="无锡销售配餐项目_SH3626Z002" state="visible" r:id="rId27"/>
-    <sheet sheetId="26" name="江苏苏州销售分公司江乾站配餐项目_合并" state="visible" r:id="rId28"/>
-    <sheet sheetId="27" name="江苏苏州销售分公司江乾站配餐项目_222200150912" state="visible" r:id="rId29"/>
-    <sheet sheetId="28" name="江苏苏州销售分公司江乾站配餐项目_SH3B25Z079" state="visible" r:id="rId30"/>
-    <sheet sheetId="29" name="苏州销售太仓实训基地" state="visible" r:id="rId31"/>
+    <sheet sheetId="4" name="宜兴度假村" state="visible" r:id="rId6"/>
+    <sheet sheetId="5" name="泰州配餐_合并" state="visible" r:id="rId7"/>
+    <sheet sheetId="6" name="泰州配餐_222200150505" state="visible" r:id="rId8"/>
+    <sheet sheetId="7" name="泰州配餐_222200150609" state="visible" r:id="rId9"/>
+    <sheet sheetId="8" name="苏州劳务输出_合并" state="visible" r:id="rId10"/>
+    <sheet sheetId="9" name="苏州劳务输出_222200150521" state="visible" r:id="rId11"/>
+    <sheet sheetId="10" name="苏州劳务输出_SH3B25Z077" state="visible" r:id="rId12"/>
+    <sheet sheetId="11" name="中油锡山配餐_合并" state="visible" r:id="rId13"/>
+    <sheet sheetId="12" name="中油锡山配餐_222200150523" state="visible" r:id="rId14"/>
+    <sheet sheetId="13" name="中油锡山配餐_SH3B25Z075" state="visible" r:id="rId15"/>
+    <sheet sheetId="14" name="太仓配餐" state="visible" r:id="rId16"/>
+    <sheet sheetId="15" name="酒店整租租赁" state="visible" r:id="rId17"/>
+    <sheet sheetId="16" name="荣巷门面租赁" state="visible" r:id="rId18"/>
+    <sheet sheetId="17" name="无锡商品销售" state="visible" r:id="rId19"/>
+    <sheet sheetId="18" name="荣巷门面能源" state="visible" r:id="rId20"/>
+    <sheet sheetId="19" name="天然气连云港配餐_合并" state="visible" r:id="rId21"/>
+    <sheet sheetId="20" name="天然气连云港配餐_222200150607" state="visible" r:id="rId22"/>
+    <sheet sheetId="21" name="天然气连云港配餐_SH3626Z001" state="visible" r:id="rId23"/>
+    <sheet sheetId="22" name="无锡润滑脂配餐" state="visible" r:id="rId24"/>
+    <sheet sheetId="23" name="无锡销售配餐_合并" state="visible" r:id="rId25"/>
+    <sheet sheetId="24" name="无锡销售配餐_222200150608" state="visible" r:id="rId26"/>
+    <sheet sheetId="25" name="无锡销售配餐_SH3626Z002" state="visible" r:id="rId27"/>
+    <sheet sheetId="26" name="苏州江乾站配餐_合并" state="visible" r:id="rId28"/>
+    <sheet sheetId="27" name="苏州江乾站配餐_222200150912" state="visible" r:id="rId29"/>
+    <sheet sheetId="28" name="苏州江乾站配餐_SH3B25Z079" state="visible" r:id="rId30"/>
+    <sheet sheetId="29" name="苏州太仓基地" state="visible" r:id="rId31"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -58,82 +58,82 @@
     <t>合计</t>
   </si>
   <si>
-    <t>宜兴度假村项目租赁项目（华东分）</t>
+    <t>宜兴度假村</t>
   </si>
   <si>
-    <t>江苏泰州销售配餐项目_合并</t>
+    <t>泰州配餐_合并</t>
   </si>
   <si>
-    <t>江苏泰州销售配餐项目_222200150505</t>
+    <t>泰州配餐_222200150505</t>
   </si>
   <si>
-    <t>江苏泰州销售配餐项目_222200150609</t>
+    <t>泰州配餐_222200150609</t>
   </si>
   <si>
-    <t>江苏苏州销售分公司劳务输出_合并</t>
+    <t>苏州劳务输出_合并</t>
   </si>
   <si>
-    <t>江苏苏州销售分公司劳务输出_222200150521</t>
+    <t>苏州劳务输出_222200150521</t>
   </si>
   <si>
-    <t>江苏苏州销售分公司劳务输出_SH3B25Z077</t>
+    <t>苏州劳务输出_SH3B25Z077</t>
   </si>
   <si>
-    <t>中油锡山石油有限公司配餐项目_合并</t>
+    <t>中油锡山配餐_合并</t>
   </si>
   <si>
-    <t>中油锡山石油有限公司配餐项目_222200150523</t>
+    <t>中油锡山配餐_222200150523</t>
   </si>
   <si>
-    <t>中油锡山石油有限公司配餐项目_SH3B25Z075</t>
+    <t>中油锡山配餐_SH3B25Z075</t>
   </si>
   <si>
-    <t>江苏太仓燃气公司配餐项目</t>
+    <t>太仓配餐</t>
   </si>
   <si>
-    <t>马山檀溪1号温特莱酒店租赁项目</t>
+    <t>酒店整租租赁</t>
   </si>
   <si>
-    <t>荣巷门面房租赁项目</t>
+    <t>荣巷门面租赁</t>
   </si>
   <si>
-    <t>无锡酒店商品销售项目</t>
+    <t>无锡商品销售</t>
   </si>
   <si>
-    <t>荣巷门面房能源转售项目</t>
+    <t>荣巷门面能源</t>
   </si>
   <si>
-    <t>天然气连云港销售分公司配餐项目_合并</t>
+    <t>天然气连云港配餐_合并</t>
   </si>
   <si>
-    <t>天然气连云港销售分公司配餐项目_222200150607</t>
+    <t>天然气连云港配餐_222200150607</t>
   </si>
   <si>
-    <t>天然气连云港销售分公司配餐项目_SH3626Z001</t>
+    <t>天然气连云港配餐_SH3626Z001</t>
   </si>
   <si>
-    <t>无锡润滑脂配餐项目</t>
+    <t>无锡润滑脂配餐</t>
   </si>
   <si>
-    <t>无锡销售配餐项目_合并</t>
+    <t>无锡销售配餐_合并</t>
   </si>
   <si>
-    <t>无锡销售配餐项目_222200150608</t>
+    <t>无锡销售配餐_222200150608</t>
   </si>
   <si>
-    <t>无锡销售配餐项目_SH3626Z002</t>
+    <t>无锡销售配餐_SH3626Z002</t>
   </si>
   <si>
-    <t>江苏苏州销售分公司江乾站配餐项目_合并</t>
+    <t>苏州江乾站配餐_合并</t>
   </si>
   <si>
-    <t>江苏苏州销售分公司江乾站配餐项目_222200150912</t>
+    <t>苏州江乾站配餐_222200150912</t>
   </si>
   <si>
-    <t>江苏苏州销售分公司江乾站配餐项目_SH3B25Z079</t>
+    <t>苏州江乾站配餐_SH3B25Z079</t>
   </si>
   <si>
-    <t>苏州销售太仓实训基地</t>
+    <t>苏州太仓基地</t>
   </si>
   <si>
     <t>合计预算执行分析（2026年08月）</t>
@@ -379,10 +379,10 @@
     <t>四、净利润</t>
   </si>
   <si>
-    <t>宜兴度假村项目租赁项目（华东分）预算执行分析（2026年08月）</t>
+    <t>宜兴度假村预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>江苏泰州销售配餐项目_合并预算执行分析（2026年08月）</t>
+    <t>泰州配餐_合并预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>上年因ERP上线提前关账，进入7个月的收入，本年是正常入8个月收入</t>
@@ -403,13 +403,13 @@
     <t>上半年为甲方举办了特色美食节活动及标准化手册等使五项费用超预算，差旅费也较预算有所增加</t>
   </si>
   <si>
-    <t>江苏泰州销售配餐项目_222200150505预算执行分析（2026年08月）</t>
+    <t>泰州配餐_222200150505预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>江苏泰州销售配餐项目_222200150609预算执行分析（2026年08月）</t>
+    <t>泰州配餐_222200150609预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>江苏苏州销售分公司劳务输出_合并预算执行分析（2026年08月）</t>
+    <t>苏州劳务输出_合并预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>上年因ERP上线提前关账，进了7个月的收入，本年是正常入8个月收入</t>
@@ -427,13 +427,13 @@
     <t>差旅手续费等</t>
   </si>
   <si>
-    <t>江苏苏州销售分公司劳务输出_222200150521预算执行分析（2026年08月）</t>
+    <t>苏州劳务输出_222200150521预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>江苏苏州销售分公司劳务输出_SH3B25Z077预算执行分析（2026年08月）</t>
+    <t>苏州劳务输出_SH3B25Z077预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>中油锡山石油有限公司配餐项目_合并预算执行分析（2026年08月）</t>
+    <t>中油锡山配餐_合并预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>上年2月此项目合同结束，因此同比收入增加</t>
@@ -454,13 +454,13 @@
     <t>本年制作了管理手册</t>
   </si>
   <si>
-    <t>中油锡山石油有限公司配餐项目_222200150523预算执行分析（2026年08月）</t>
+    <t>中油锡山配餐_222200150523预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>中油锡山石油有限公司配餐项目_SH3B25Z075预算执行分析（2026年08月）</t>
+    <t>中油锡山配餐_SH3B25Z075预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>江苏太仓燃气公司配餐项目预算执行分析（2026年08月）</t>
+    <t>太仓配餐预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>此项目为含食材项目，服务费为人工部分的百分之十，人工成本部分甲方固定支付，餐费为月累计实际每日人数据实结算，业主方存在休假人员致使实际就餐人数未达预算，遂餐费部分收入比预算减少0.02万元，</t>
@@ -475,7 +475,7 @@
     <t>本年发生油烟机清洗费</t>
   </si>
   <si>
-    <t>马山檀溪1号温特莱酒店租赁项目预算执行分析（2026年08月）</t>
+    <t>酒店整租租赁预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>收入未完成预算主要是本年未进收入，</t>
@@ -496,7 +496,7 @@
     <t>信用减值损失的增加是因为本年有353万应收账款账龄超过1年，信用减值计提了85.5万。</t>
   </si>
   <si>
-    <t>荣巷门面房租赁项目预算执行分析（2026年08月）</t>
+    <t>荣巷门面租赁预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>荣巷2025年全部出租，因此同比增加0.9万收入,</t>
@@ -514,7 +514,7 @@
     <t>预算上有空租3间，本年实际全部出租后租金上涨，使从租计征的房产税增加</t>
   </si>
   <si>
-    <t>无锡酒店商品销售项目预算执行分析（2026年08月）</t>
+    <t>无锡商品销售预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>上半年完成杨梅销售152筐，创收2.3万元；端午粽子78盒，创收0.9万元；开展消费帮扶采购4.6万元。</t>
@@ -523,7 +523,7 @@
     <t>商品销售未达预期</t>
   </si>
   <si>
-    <t>荣巷门面房能源转售项目预算执行分析（2026年08月）</t>
+    <t>荣巷门面能源预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>年初一间门面房退租重新招租，使转售水电的收入成本有变动</t>
@@ -532,7 +532,7 @@
     <t>门面房全部出租，能源转售项目原则上无利润。</t>
   </si>
   <si>
-    <t>天然气连云港销售分公司配餐项目_合并预算执行分析（2026年08月）</t>
+    <t>天然气连云港配餐_合并预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>上年同期有加班费，合同于6月14日转入常州后，按收入配比原则进了半个月收入，综上同比收入减少2.8万元</t>
@@ -556,13 +556,13 @@
     <t>本年差旅费比预算增加</t>
   </si>
   <si>
-    <t>天然气连云港销售分公司配餐项目_222200150607预算执行分析（2026年08月）</t>
+    <t>天然气连云港配餐_222200150607预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>天然气连云港销售分公司配餐项目_SH3626Z001预算执行分析（2026年08月）</t>
+    <t>天然气连云港配餐_SH3626Z001预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>无锡润滑脂配餐项目预算执行分析（2026年08月）</t>
+    <t>无锡润滑脂配餐预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>本年新签合同减少了一名管理人员，使合同金额减少3.24万元，上年同期加班费同比减少0.69万。</t>
@@ -577,7 +577,7 @@
     <t>上半年制作了管理手册</t>
   </si>
   <si>
-    <t>无锡销售配餐项目_合并预算执行分析（2026年08月）</t>
+    <t>无锡销售配餐_合并预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>收入同比减少80.17万元主要是去年续签合同时取消了加油站的服务项目。</t>
@@ -598,13 +598,13 @@
     <t>因属于先服务再结算，上年同期该项目仍在无锡核算，因此有计提</t>
   </si>
   <si>
-    <t>无锡销售配餐项目_222200150608预算执行分析（2026年08月）</t>
+    <t>无锡销售配餐_222200150608预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>无锡销售配餐项目_SH3626Z002预算执行分析（2026年08月）</t>
+    <t>无锡销售配餐_SH3626Z002预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>江苏苏州销售分公司江乾站配餐项目_合并预算执行分析（2026年08月）</t>
+    <t>苏州江乾站配餐_合并预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>主要原因为华兴劳务公司按照应收1.35%缴纳残保金</t>
@@ -613,13 +613,13 @@
     <t>本年预算基数以项目合同测算表为基数，实际经营过程中目前存在使用退休返聘人员等情况，致使人工成本收入未完全按照测算表进度推进，若后续业主方要求更换人员，结余费用需进行使用，如替换缴纳社保人员。及此项目（高温、劳保、体检）三项费用，预算时为全年每月均摊，实际上半年未发生，三项费用3人年共计（4770元/12月*6月=2384元），上半年节省0.12万元，本年实际发生福利费0.39万元，华兴劳务公司按照应收1.35%缴纳残保金。上年2月发生工服采购款0.05万元。遂人工成本同比增加0.2万元，比预算减少0.5万元，</t>
   </si>
   <si>
-    <t>江苏苏州销售分公司江乾站配餐项目_222200150912预算执行分析（2026年08月）</t>
+    <t>苏州江乾站配餐_222200150912预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>江苏苏州销售分公司江乾站配餐项目_SH3B25Z079预算执行分析（2026年08月）</t>
+    <t>苏州江乾站配餐_SH3B25Z079预算执行分析（2026年08月）</t>
   </si>
   <si>
-    <t>苏州销售太仓实训基地预算执行分析（2026年08月）</t>
+    <t>苏州太仓基地预算执行分析（2026年08月）</t>
   </si>
   <si>
     <t>2025年11月新增项目</t>
@@ -8914,7 +8914,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="5" t="str">
-        <f>HYPERLINK("#'宜兴度假村项目租赁项目（华东分）'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'宜兴度假村'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -8924,7 +8924,7 @@
         <v>6</v>
       </c>
       <c r="C5" s="5" t="str">
-        <f>HYPERLINK("#'江苏泰州销售配餐项目_合并'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'泰州配餐_合并'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -8934,7 +8934,7 @@
         <v>7</v>
       </c>
       <c r="C6" s="5" t="str">
-        <f>HYPERLINK("#'江苏泰州销售配餐项目_222200150505'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'泰州配餐_222200150505'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -8944,7 +8944,7 @@
         <v>8</v>
       </c>
       <c r="C7" s="5" t="str">
-        <f>HYPERLINK("#'江苏泰州销售配餐项目_222200150609'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'泰州配餐_222200150609'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -8954,7 +8954,7 @@
         <v>9</v>
       </c>
       <c r="C8" s="5" t="str">
-        <f>HYPERLINK("#'江苏苏州销售分公司劳务输出_合并'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'苏州劳务输出_合并'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -8964,7 +8964,7 @@
         <v>10</v>
       </c>
       <c r="C9" s="5" t="str">
-        <f>HYPERLINK("#'江苏苏州销售分公司劳务输出_222200150521'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'苏州劳务输出_222200150521'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -8974,7 +8974,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="5" t="str">
-        <f>HYPERLINK("#'江苏苏州销售分公司劳务输出_SH3B25Z077'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'苏州劳务输出_SH3B25Z077'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -8984,7 +8984,7 @@
         <v>12</v>
       </c>
       <c r="C11" s="5" t="str">
-        <f>HYPERLINK("#'中油锡山石油有限公司配餐项目_合并'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'中油锡山配餐_合并'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
         <v>13</v>
       </c>
       <c r="C12" s="5" t="str">
-        <f>HYPERLINK("#'中油锡山石油有限公司配餐项目_222200150523'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'中油锡山配餐_222200150523'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -9004,7 +9004,7 @@
         <v>14</v>
       </c>
       <c r="C13" s="5" t="str">
-        <f>HYPERLINK("#'中油锡山石油有限公司配餐项目_SH3B25Z075'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'中油锡山配餐_SH3B25Z075'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -9014,7 +9014,7 @@
         <v>15</v>
       </c>
       <c r="C14" s="5" t="str">
-        <f>HYPERLINK("#'江苏太仓燃气公司配餐项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'太仓配餐'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -9024,7 +9024,7 @@
         <v>16</v>
       </c>
       <c r="C15" s="5" t="str">
-        <f>HYPERLINK("#'马山檀溪1号温特莱酒店租赁项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'酒店整租租赁'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -9034,7 +9034,7 @@
         <v>17</v>
       </c>
       <c r="C16" s="5" t="str">
-        <f>HYPERLINK("#'荣巷门面房租赁项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'荣巷门面租赁'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -9044,7 +9044,7 @@
         <v>18</v>
       </c>
       <c r="C17" s="5" t="str">
-        <f>HYPERLINK("#'无锡酒店商品销售项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'无锡商品销售'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -9054,7 +9054,7 @@
         <v>19</v>
       </c>
       <c r="C18" s="5" t="str">
-        <f>HYPERLINK("#'荣巷门面房能源转售项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'荣巷门面能源'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -9064,7 +9064,7 @@
         <v>20</v>
       </c>
       <c r="C19" s="5" t="str">
-        <f>HYPERLINK("#'天然气连云港销售分公司配餐项目_合并'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'天然气连云港配餐_合并'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -9074,7 +9074,7 @@
         <v>21</v>
       </c>
       <c r="C20" s="5" t="str">
-        <f>HYPERLINK("#'天然气连云港销售分公司配餐项目_222200150607'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'天然气连云港配餐_222200150607'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -9084,7 +9084,7 @@
         <v>22</v>
       </c>
       <c r="C21" s="5" t="str">
-        <f>HYPERLINK("#'天然气连云港销售分公司配餐项目_SH3626Z001'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'天然气连云港配餐_SH3626Z001'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -9094,7 +9094,7 @@
         <v>23</v>
       </c>
       <c r="C22" s="5" t="str">
-        <f>HYPERLINK("#'无锡润滑脂配餐项目'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'无锡润滑脂配餐'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -9104,7 +9104,7 @@
         <v>24</v>
       </c>
       <c r="C23" s="5" t="str">
-        <f>HYPERLINK("#'无锡销售配餐项目_合并'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'无锡销售配餐_合并'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -9114,7 +9114,7 @@
         <v>25</v>
       </c>
       <c r="C24" s="5" t="str">
-        <f>HYPERLINK("#'无锡销售配餐项目_222200150608'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'无锡销售配餐_222200150608'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -9124,7 +9124,7 @@
         <v>26</v>
       </c>
       <c r="C25" s="5" t="str">
-        <f>HYPERLINK("#'无锡销售配餐项目_SH3626Z002'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'无锡销售配餐_SH3626Z002'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
         <v>27</v>
       </c>
       <c r="C26" s="5" t="str">
-        <f>HYPERLINK("#'江苏苏州销售分公司江乾站配餐项目_合并'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'苏州江乾站配餐_合并'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -9144,7 +9144,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="5" t="str">
-        <f>HYPERLINK("#'江苏苏州销售分公司江乾站配餐项目_222200150912'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'苏州江乾站配餐_222200150912'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -9154,7 +9154,7 @@
         <v>29</v>
       </c>
       <c r="C28" s="5" t="str">
-        <f>HYPERLINK("#'江苏苏州销售分公司江乾站配餐项目_SH3B25Z079'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'苏州江乾站配餐_SH3B25Z079'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
@@ -9164,7 +9164,7 @@
         <v>30</v>
       </c>
       <c r="C29" s="5" t="str">
-        <f>HYPERLINK("#'苏州销售太仓实训基地'!A1","点击跳转 ➔")</f>
+        <f>HYPERLINK("#'苏州太仓基地'!A1","点击跳转 ➔")</f>
         <v>点击跳转 ➔</v>
       </c>
     </row>
